--- a/autoIt/ImportFiles/TestSmokeBuyigRatesImport.xlsx
+++ b/autoIt/ImportFiles/TestSmokeBuyigRatesImport.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="348">
   <si>
     <t>ItemName</t>
   </si>
@@ -223,6 +223,846 @@
   </si>
   <si>
     <t>07/01/2023</t>
+  </si>
+  <si>
+    <t>13/02/2023</t>
+  </si>
+  <si>
+    <t>18/02/2023</t>
+  </si>
+  <si>
+    <t>20/02/2023</t>
+  </si>
+  <si>
+    <t>25/02/2023</t>
+  </si>
+  <si>
+    <t>21/02/2023</t>
+  </si>
+  <si>
+    <t>26/02/2023</t>
+  </si>
+  <si>
+    <t>22/02/2023</t>
+  </si>
+  <si>
+    <t>27/02/2023</t>
+  </si>
+  <si>
+    <t>04/03/2023</t>
+  </si>
+  <si>
+    <t>28/02/2023</t>
+  </si>
+  <si>
+    <t>05/03/2023</t>
+  </si>
+  <si>
+    <t>01/03/2023</t>
+  </si>
+  <si>
+    <t>06/03/2023</t>
+  </si>
+  <si>
+    <t>10/03/2023</t>
+  </si>
+  <si>
+    <t>11/03/2023</t>
+  </si>
+  <si>
+    <t>08/03/2023</t>
+  </si>
+  <si>
+    <t>13/03/2023</t>
+  </si>
+  <si>
+    <t>23/03/2023</t>
+  </si>
+  <si>
+    <t>24/03/2023</t>
+  </si>
+  <si>
+    <t>06/04/2023</t>
+  </si>
+  <si>
+    <t>11/04/2023</t>
+  </si>
+  <si>
+    <t>12/04/2023</t>
+  </si>
+  <si>
+    <t>18/04/2023</t>
+  </si>
+  <si>
+    <t>23/04/2023</t>
+  </si>
+  <si>
+    <t>20/04/2023</t>
+  </si>
+  <si>
+    <t>25/04/2023</t>
+  </si>
+  <si>
+    <t>06/05/2023</t>
+  </si>
+  <si>
+    <t>11/05/2023</t>
+  </si>
+  <si>
+    <t>10/05/2023</t>
+  </si>
+  <si>
+    <t>15/05/2023</t>
+  </si>
+  <si>
+    <t>14/06/2023</t>
+  </si>
+  <si>
+    <t>19/06/2023</t>
+  </si>
+  <si>
+    <t>04/07/2023</t>
+  </si>
+  <si>
+    <t>09/07/2023</t>
+  </si>
+  <si>
+    <t>10/08/2023</t>
+  </si>
+  <si>
+    <t>15/08/2023</t>
+  </si>
+  <si>
+    <t>23/08/2023</t>
+  </si>
+  <si>
+    <t>28/08/2023</t>
+  </si>
+  <si>
+    <t>29/08/2023</t>
+  </si>
+  <si>
+    <t>03/09/2023</t>
+  </si>
+  <si>
+    <t>30/10/2023</t>
+  </si>
+  <si>
+    <t>04/11/2023</t>
+  </si>
+  <si>
+    <t>02/11/2023</t>
+  </si>
+  <si>
+    <t>07/11/2023</t>
+  </si>
+  <si>
+    <t>28/11/2023</t>
+  </si>
+  <si>
+    <t>03/12/2023</t>
+  </si>
+  <si>
+    <t>29/11/2023</t>
+  </si>
+  <si>
+    <t>04/12/2023</t>
+  </si>
+  <si>
+    <t>06/12/2023</t>
+  </si>
+  <si>
+    <t>11/12/2023</t>
+  </si>
+  <si>
+    <t>29/12/2023</t>
+  </si>
+  <si>
+    <t>03/01/2024</t>
+  </si>
+  <si>
+    <t>23/01/2024</t>
+  </si>
+  <si>
+    <t>28/01/2024</t>
+  </si>
+  <si>
+    <t>24/01/2024</t>
+  </si>
+  <si>
+    <t>29/01/2024</t>
+  </si>
+  <si>
+    <t>07/02/2024</t>
+  </si>
+  <si>
+    <t>12/02/2024</t>
+  </si>
+  <si>
+    <t>17/02/2024</t>
+  </si>
+  <si>
+    <t>15/02/2024</t>
+  </si>
+  <si>
+    <t>20/02/2024</t>
+  </si>
+  <si>
+    <t>25/02/2024</t>
+  </si>
+  <si>
+    <t>27/02/2024</t>
+  </si>
+  <si>
+    <t>03/03/2024</t>
+  </si>
+  <si>
+    <t>29/02/2024</t>
+  </si>
+  <si>
+    <t>05/03/2024</t>
+  </si>
+  <si>
+    <t>11/03/2024</t>
+  </si>
+  <si>
+    <t>16/03/2024</t>
+  </si>
+  <si>
+    <t>03/11/2024</t>
+  </si>
+  <si>
+    <t>03/16/2024</t>
+  </si>
+  <si>
+    <t>12/03/2024</t>
+  </si>
+  <si>
+    <t>17/03/2024</t>
+  </si>
+  <si>
+    <t>13/03/2024</t>
+  </si>
+  <si>
+    <t>18/03/2024</t>
+  </si>
+  <si>
+    <t>23/03/2024</t>
+  </si>
+  <si>
+    <t>26/04/2024</t>
+  </si>
+  <si>
+    <t>01/05/2024</t>
+  </si>
+  <si>
+    <t>03/05/2024</t>
+  </si>
+  <si>
+    <t>08/05/2024</t>
+  </si>
+  <si>
+    <t>14/05/2024</t>
+  </si>
+  <si>
+    <t>19/05/2024</t>
+  </si>
+  <si>
+    <t>16/05/2024</t>
+  </si>
+  <si>
+    <t>21/05/2024</t>
+  </si>
+  <si>
+    <t>17/05/2024</t>
+  </si>
+  <si>
+    <t>22/05/2024</t>
+  </si>
+  <si>
+    <t>18/05/2024</t>
+  </si>
+  <si>
+    <t>23/05/2024</t>
+  </si>
+  <si>
+    <t>26/05/2024</t>
+  </si>
+  <si>
+    <t>27/05/2024</t>
+  </si>
+  <si>
+    <t>01/06/2024</t>
+  </si>
+  <si>
+    <t>06/06/2024</t>
+  </si>
+  <si>
+    <t>11/06/2024</t>
+  </si>
+  <si>
+    <t>16/06/2024</t>
+  </si>
+  <si>
+    <t>06/28/2024</t>
+  </si>
+  <si>
+    <t>07/03/2024</t>
+  </si>
+  <si>
+    <t>07/08/2024</t>
+  </si>
+  <si>
+    <t>07/13/2024</t>
+  </si>
+  <si>
+    <t>08/07/2024</t>
+  </si>
+  <si>
+    <t>13/07/2024</t>
+  </si>
+  <si>
+    <t>30/07/2024</t>
+  </si>
+  <si>
+    <t>04/08/2024</t>
+  </si>
+  <si>
+    <t>01/08/2024</t>
+  </si>
+  <si>
+    <t>06/08/2024</t>
+  </si>
+  <si>
+    <t>08/08/2024</t>
+  </si>
+  <si>
+    <t>13/08/2024</t>
+  </si>
+  <si>
+    <t>19/08/2024</t>
+  </si>
+  <si>
+    <t>24/08/2024</t>
+  </si>
+  <si>
+    <t>21/08/2024</t>
+  </si>
+  <si>
+    <t>26/08/2024</t>
+  </si>
+  <si>
+    <t>31/08/2024</t>
+  </si>
+  <si>
+    <t>28/08/2024</t>
+  </si>
+  <si>
+    <t>02/09/2024</t>
+  </si>
+  <si>
+    <t>30/08/2024</t>
+  </si>
+  <si>
+    <t>04/09/2024</t>
+  </si>
+  <si>
+    <t>05/09/2024</t>
+  </si>
+  <si>
+    <t>03/09/2024</t>
+  </si>
+  <si>
+    <t>08/09/2024</t>
+  </si>
+  <si>
+    <t>09/09/2024</t>
+  </si>
+  <si>
+    <t>10/09/2024</t>
+  </si>
+  <si>
+    <t>20/09/2024</t>
+  </si>
+  <si>
+    <t>25/09/2024</t>
+  </si>
+  <si>
+    <t>23/09/2024</t>
+  </si>
+  <si>
+    <t>28/09/2024</t>
+  </si>
+  <si>
+    <t>23/10/2024</t>
+  </si>
+  <si>
+    <t>28/10/2024</t>
+  </si>
+  <si>
+    <t>18/11/2024</t>
+  </si>
+  <si>
+    <t>23/11/2024</t>
+  </si>
+  <si>
+    <t>19/11/2024</t>
+  </si>
+  <si>
+    <t>24/11/2024</t>
+  </si>
+  <si>
+    <t>22/11/2024</t>
+  </si>
+  <si>
+    <t>27/11/2024</t>
+  </si>
+  <si>
+    <t>25/11/2024</t>
+  </si>
+  <si>
+    <t>30/11/2024</t>
+  </si>
+  <si>
+    <t>26/11/2024</t>
+  </si>
+  <si>
+    <t>01/12/2024</t>
+  </si>
+  <si>
+    <t>12/12/2024</t>
+  </si>
+  <si>
+    <t>17/12/2024</t>
+  </si>
+  <si>
+    <t>18/12/2024</t>
+  </si>
+  <si>
+    <t>23/12/2024</t>
+  </si>
+  <si>
+    <t>28/12/2024</t>
+  </si>
+  <si>
+    <t>25/12/2024</t>
+  </si>
+  <si>
+    <t>30/12/2024</t>
+  </si>
+  <si>
+    <t>27/12/2024</t>
+  </si>
+  <si>
+    <t>01/01/2025</t>
+  </si>
+  <si>
+    <t>08/01/2025</t>
+  </si>
+  <si>
+    <t>13/01/2025</t>
+  </si>
+  <si>
+    <t>17/01/2025</t>
+  </si>
+  <si>
+    <t>22/01/2025</t>
+  </si>
+  <si>
+    <t>18/01/2025</t>
+  </si>
+  <si>
+    <t>23/01/2025</t>
+  </si>
+  <si>
+    <t>21/01/2025</t>
+  </si>
+  <si>
+    <t>26/01/2025</t>
+  </si>
+  <si>
+    <t>28/01/2025</t>
+  </si>
+  <si>
+    <t>02/02/2025</t>
+  </si>
+  <si>
+    <t>05/02/2025</t>
+  </si>
+  <si>
+    <t>10/02/2025</t>
+  </si>
+  <si>
+    <t>06/02/2025</t>
+  </si>
+  <si>
+    <t>11/02/2025</t>
+  </si>
+  <si>
+    <t>19/02/2025</t>
+  </si>
+  <si>
+    <t>24/02/2025</t>
+  </si>
+  <si>
+    <t>25/02/2025</t>
+  </si>
+  <si>
+    <t>02/03/2025</t>
+  </si>
+  <si>
+    <t>07/03/2025</t>
+  </si>
+  <si>
+    <t>09/03/2025</t>
+  </si>
+  <si>
+    <t>14/03/2025</t>
+  </si>
+  <si>
+    <t>09/04/2025</t>
+  </si>
+  <si>
+    <t>14/04/2025</t>
+  </si>
+  <si>
+    <t>28/04/2025</t>
+  </si>
+  <si>
+    <t>03/05/2025</t>
+  </si>
+  <si>
+    <t>07/05/2025</t>
+  </si>
+  <si>
+    <t>12/05/2025</t>
+  </si>
+  <si>
+    <t>15/05/2025</t>
+  </si>
+  <si>
+    <t>20/05/2025</t>
+  </si>
+  <si>
+    <t>23/05/2025</t>
+  </si>
+  <si>
+    <t>28/05/2025</t>
+  </si>
+  <si>
+    <t>29/05/2025</t>
+  </si>
+  <si>
+    <t>03/06/2025</t>
+  </si>
+  <si>
+    <t>31/05/2025</t>
+  </si>
+  <si>
+    <t>05/06/2025</t>
+  </si>
+  <si>
+    <t>02/06/2025</t>
+  </si>
+  <si>
+    <t>07/06/2025</t>
+  </si>
+  <si>
+    <t>10/06/2025</t>
+  </si>
+  <si>
+    <t>12/06/2025</t>
+  </si>
+  <si>
+    <t>15/06/2025</t>
+  </si>
+  <si>
+    <t>26/06/2025</t>
+  </si>
+  <si>
+    <t>01/07/2025</t>
+  </si>
+  <si>
+    <t>02/07/2025</t>
+  </si>
+  <si>
+    <t>07/07/2025</t>
+  </si>
+  <si>
+    <t>16/07/2025</t>
+  </si>
+  <si>
+    <t>21/07/2025</t>
+  </si>
+  <si>
+    <t>30/07/2025</t>
+  </si>
+  <si>
+    <t>04/08/2025</t>
+  </si>
+  <si>
+    <t>05/08/2025</t>
+  </si>
+  <si>
+    <t>10/08/2025</t>
+  </si>
+  <si>
+    <t>08/08/2025</t>
+  </si>
+  <si>
+    <t>13/08/2025</t>
+  </si>
+  <si>
+    <t>09/08/2025</t>
+  </si>
+  <si>
+    <t>14/08/2025</t>
+  </si>
+  <si>
+    <t>11/08/2025</t>
+  </si>
+  <si>
+    <t>16/08/2025</t>
+  </si>
+  <si>
+    <t>12/08/2025</t>
+  </si>
+  <si>
+    <t>17/08/2025</t>
+  </si>
+  <si>
+    <t>19/08/2025</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>23/08/2025</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
+  </si>
+  <si>
+    <t>24/08/2025</t>
+  </si>
+  <si>
+    <t>29/08/2025</t>
+  </si>
+  <si>
+    <t>01/09/2025</t>
+  </si>
+  <si>
+    <t>30/08/2025</t>
+  </si>
+  <si>
+    <t>04/09/2025</t>
+  </si>
+  <si>
+    <t>03/09/2025</t>
+  </si>
+  <si>
+    <t>08/09/2025</t>
+  </si>
+  <si>
+    <t>09/09/2025</t>
+  </si>
+  <si>
+    <t>13/09/2025</t>
+  </si>
+  <si>
+    <t>10/09/2025</t>
+  </si>
+  <si>
+    <t>15/09/2025</t>
+  </si>
+  <si>
+    <t>18/09/2025</t>
+  </si>
+  <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
+    <t>21/09/2025</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>24/09/2025</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>28/09/2025</t>
+  </si>
+  <si>
+    <t>26/09/2025</t>
+  </si>
+  <si>
+    <t>01/10/2025</t>
+  </si>
+  <si>
+    <t>27/09/2025</t>
+  </si>
+  <si>
+    <t>02/10/2025</t>
+  </si>
+  <si>
+    <t>07/10/2025</t>
+  </si>
+  <si>
+    <t>12/10/2025</t>
+  </si>
+  <si>
+    <t>08/10/2025</t>
+  </si>
+  <si>
+    <t>13/10/2025</t>
+  </si>
+  <si>
+    <t>09/10/2025</t>
+  </si>
+  <si>
+    <t>14/10/2025</t>
+  </si>
+  <si>
+    <t>10/10/2025</t>
+  </si>
+  <si>
+    <t>15/10/2025</t>
+  </si>
+  <si>
+    <t>11/10/2025</t>
+  </si>
+  <si>
+    <t>16/10/2025</t>
+  </si>
+  <si>
+    <t>19/10/2025</t>
+  </si>
+  <si>
+    <t>24/10/2025</t>
+  </si>
+  <si>
+    <t>29/10/2025</t>
+  </si>
+  <si>
+    <t>03/11/2025</t>
+  </si>
+  <si>
+    <t>04/11/2025</t>
+  </si>
+  <si>
+    <t>09/11/2025</t>
+  </si>
+  <si>
+    <t>08/11/2025</t>
+  </si>
+  <si>
+    <t>13/11/2025</t>
+  </si>
+  <si>
+    <t>18/11/2025</t>
+  </si>
+  <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>24/11/2025</t>
+  </si>
+  <si>
+    <t>29/11/2025</t>
+  </si>
+  <si>
+    <t>27/11/2025</t>
+  </si>
+  <si>
+    <t>02/12/2025</t>
+  </si>
+  <si>
+    <t>07/12/2025</t>
+  </si>
+  <si>
+    <t>03/12/2025</t>
+  </si>
+  <si>
+    <t>08/12/2025</t>
+  </si>
+  <si>
+    <t>15/12/2025</t>
+  </si>
+  <si>
+    <t>20/12/2025</t>
+  </si>
+  <si>
+    <t>19/12/2025</t>
+  </si>
+  <si>
+    <t>24/12/2025</t>
+  </si>
+  <si>
+    <t>23/12/2025</t>
+  </si>
+  <si>
+    <t>28/12/2025</t>
+  </si>
+  <si>
+    <t>29/12/2025</t>
+  </si>
+  <si>
+    <t>03/01/2026</t>
+  </si>
+  <si>
+    <t>08/01/2026</t>
+  </si>
+  <si>
+    <t>30/01/2026</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>31/01/2026</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>01/02/2026</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>08/03/2026</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>14/03/2026</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>28/03/2026</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>12/04/2026</t>
   </si>
 </sst>
 </file>
@@ -641,13 +1481,13 @@
         <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>346</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>347</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>28</v>
@@ -712,13 +1552,13 @@
         <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>346</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>347</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>28</v>
